--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,77 +5415,77 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.69791666666</v>
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,77 +5534,77 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI54"/>
+  <dimension ref="A1:AI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>5.24</v>
       </c>
       <c r="N19" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>5.24</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46090.64583333334</v>
+        <v>46090.625</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46090.66666666666</v>
+        <v>46090.64583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46090.69791666666</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="43">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,77 +5534,77 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N43" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.69791666666</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -5735,27 +5735,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,80 +5772,80 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46090.70833333334</v>
+        <v>46090.69791666666</v>
       </c>
     </row>
     <row r="46">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46090.71875</v>
+        <v>46090.70833333334</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46090.75</v>
+        <v>46090.71875</v>
       </c>
     </row>
     <row r="48">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46090.83333333334</v>
+        <v>46090.75</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46090.85416666666</v>
+        <v>46090.83333333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46090.875</v>
+        <v>46090.85416666666</v>
       </c>
     </row>
     <row r="52">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6806,116 +6806,235 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>46090.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="3" t="n">
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
         <v>46090.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.625</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.69791666666</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M19" t="n">
-        <v>5.24</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3881,64 +3881,64 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,77 +5534,77 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.69791666666</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N44" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>3.91</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>4.38</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>5.24</v>
       </c>
       <c r="N19" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N21" t="n">
         <v>9.75</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N43" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.69791666666</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N19" t="n">
         <v>9.75</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="N21" t="n">
         <v>9.75</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N28" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4119,64 +4119,64 @@
         <v>2.19</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.64583333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI55"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="N19" t="n">
         <v>9.75</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>5.24</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6678,363 +6678,6 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46090.875</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Neftchi</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Andijan</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="3" t="n">
-        <v>46090.875</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Pakhtakor</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Navbahor</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="3" t="n">
-        <v>46090.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="3" t="n">
         <v>46090.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46090.4375</v>
+        <v>46090.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46090.4375</v>
+        <v>46090.41666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.91</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>4.38</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46090.45833333334</v>
+        <v>46090.4375</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46090.47916666666</v>
+        <v>46090.4375</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46090.5</v>
+        <v>46090.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46090.5</v>
+        <v>46090.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46090.5</v>
+        <v>46090.47916666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46090.54166666666</v>
+        <v>46090.5</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46090.54166666666</v>
+        <v>46090.5</v>
       </c>
     </row>
     <row r="21">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46090.5625</v>
+        <v>46090.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.24</v>
+        <v>5.24</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>9.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46090.5625</v>
+        <v>46090.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46090.58333333334</v>
+        <v>46090.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46090.58333333334</v>
+        <v>46090.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46090.58333333334</v>
+        <v>46090.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46090.625</v>
+        <v>46090.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46090.625</v>
+        <v>46090.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.71</v>
+        <v>3.12</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46090.625</v>
+        <v>46090.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,80 +4106,80 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.69</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>5.25</v>
+        <v>6.15</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46090.64583333334</v>
+        <v>46090.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46090.66666666666</v>
+        <v>46090.625</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46090.66666666666</v>
+        <v>46090.625</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.625</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,80 +4582,80 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.64583333334</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5595,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46090.69791666666</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="44">
@@ -5616,27 +5616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,76 +5657,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46090.69791666666</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="45">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46090.69791666666</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="46">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46090.70833333334</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,76 +6014,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.38</v>
+        <v>2.87</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46090.71875</v>
+        <v>46090.69791666666</v>
       </c>
     </row>
     <row r="48">
@@ -6092,27 +6092,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46090.75</v>
+        <v>46090.69791666666</v>
       </c>
     </row>
     <row r="49">
@@ -6211,27 +6211,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46090.75</v>
+        <v>46090.69791666666</v>
       </c>
     </row>
     <row r="50">
@@ -6330,27 +6330,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46090.83333333334</v>
+        <v>46090.70833333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,27 +6449,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46090.85416666666</v>
+        <v>46090.71875</v>
       </c>
     </row>
     <row r="52">
@@ -6568,116 +6568,592 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="n">
+        <v>46090.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
+        <v>46090.75</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>46090.83333333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>46090.85416666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="L56" t="n">
         <v>1.63</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M56" t="n">
         <v>3.72</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N56" t="n">
         <v>5.34</v>
       </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="3" t="n">
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
         <v>46090.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>3.12</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>10.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="N22" t="n">
         <v>9.75</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
         <v>9.75</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>3.12</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="O30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.91</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N47" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>3.58</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N30" t="n">
-        <v>3.12</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>5.24</v>
+        <v>3.18</v>
       </c>
       <c r="N22" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.58</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N24" t="n">
         <v>9.75</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>3.12</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="O30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>4.53</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>6.23</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.33</v>
+        <v>1.51</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>4.53</v>
       </c>
       <c r="N43" t="n">
-        <v>1.8</v>
+        <v>6.23</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N49" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="N24" t="n">
         <v>9.75</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>3.58</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>3.76</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>5.24</v>
       </c>
       <c r="N23" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>5.24</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>3.91</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>4.38</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>10.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
         <v>9.75</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>5.24</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.58</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="M33" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N24" t="n">
         <v>9.75</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.2</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46090.47916666666</v>
+        <v>46090.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46090.5</v>
+        <v>46090.47916666666</v>
       </c>
     </row>
     <row r="20">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46090.54166666666</v>
+        <v>46090.5</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="N22" t="n">
         <v>9.75</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46090.5625</v>
+        <v>46090.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46090.58333333334</v>
+        <v>46090.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46090.625</v>
+        <v>46090.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N34" t="n">
-        <v>3.76</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,80 +4582,80 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.19</v>
+        <v>3.76</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46090.64583333334</v>
+        <v>46090.625</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,80 +4701,80 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46090.66666666666</v>
+        <v>46090.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46090.6875</v>
+        <v>46090.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.33</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>1.8</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>4.53</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6.23</v>
+        <v>5.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46090.69791666666</v>
+        <v>46090.6875</v>
       </c>
     </row>
     <row r="48">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6428,10 +6428,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46090.70833333334</v>
+        <v>46090.69791666666</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46090.71875</v>
+        <v>46090.70833333334</v>
       </c>
     </row>
     <row r="52">
@@ -6568,27 +6568,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46090.75</v>
+        <v>46090.71875</v>
       </c>
     </row>
     <row r="53">

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>10.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="N22" t="n">
-        <v>9.75</v>
+        <v>3.06</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
-        <v>3.06</v>
+        <v>9.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>3.58</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.58</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>3.12</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>3.76</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N35" t="n">
-        <v>3.76</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="M2" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="N2" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -668,19 +668,19 @@
         <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>4.45</v>
+        <v>3.76</v>
       </c>
       <c r="P2" t="n">
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="T2" t="n">
         <v>4.25</v>
@@ -698,16 +698,16 @@
         <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
         <v>6.25</v>
@@ -725,7 +725,7 @@
         <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -2215,64 +2215,64 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
         <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.45</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
         <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
         <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="M2" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="O2" t="n">
         <v>3.76</v>
@@ -695,16 +695,16 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y2" t="n">
         <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.28</v>
@@ -713,7 +713,7 @@
         <v>6.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE2" t="n">
         <v>2.43</v>
@@ -725,7 +725,7 @@
         <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -1052,13 +1052,13 @@
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>1.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AA5" t="n">
         <v>2.56</v>
@@ -1079,7 +1079,7 @@
         <v>1.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
         <v>1.72</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2569,7 +2569,7 @@
         <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>4.72</v>
       </c>
       <c r="O18" t="n">
         <v>2.57</v>
@@ -2599,7 +2599,7 @@
         <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
         <v>1.36</v>
@@ -2608,16 +2608,16 @@
         <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
         <v>1.98</v>
@@ -2629,7 +2629,7 @@
         <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3762,64 +3762,64 @@
         <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>6.15</v>
+        <v>6.45</v>
       </c>
       <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.06</v>
       </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="M29" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4357,64 +4357,64 @@
         <v>3.71</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N34" t="n">
-        <v>3.76</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.89</v>
+        <v>4.75</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
         <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5071,64 +5071,64 @@
         <v>6.23</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5785,64 +5785,64 @@
         <v>1.8</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5904,64 +5904,64 @@
         <v>5.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -6023,64 +6023,64 @@
         <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6380,40 +6380,40 @@
         <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA50" t="n">
         <v>2.2</v>
@@ -6422,10 +6422,10 @@
         <v>1.66</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
         <v>1.95</v>
@@ -6434,10 +6434,10 @@
         <v>1.8</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6618,64 +6618,64 @@
         <v>3.38</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46090.71875</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
         <v>3.91</v>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2215,64 +2215,64 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
         <v>2.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M25" t="n">
-        <v>5.24</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>9.75</v>
+        <v>7.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.3</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.12</v>
-      </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.33</v>
+        <v>1.57</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="O45" t="n">
-        <v>5.54</v>
+        <v>2.28</v>
       </c>
       <c r="P45" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.5</v>
+        <v>5.85</v>
       </c>
       <c r="R45" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="T45" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U45" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
         <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.25</v>
+        <v>3.82</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,37 +5895,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="P46" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.85</v>
+        <v>4.78</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S46" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T46" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U46" t="n">
         <v>1.28</v>
       </c>
       <c r="V46" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W46" t="n">
         <v>1.01</v>
@@ -5940,28 +5940,28 @@
         <v>2.83</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB46" t="n">
         <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="AD46" t="n">
         <v>1.18</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N47" t="n">
         <v>1.8</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N47" t="n">
-        <v>4</v>
-      </c>
       <c r="O47" t="n">
-        <v>2.49</v>
+        <v>5.54</v>
       </c>
       <c r="P47" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.78</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T47" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U47" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W47" t="n">
         <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.81</v>
+        <v>1.14</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6142,64 +6142,64 @@
         <v>2.23</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46090.70833333334</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="M2" t="n">
         <v>2.93</v>
@@ -695,7 +695,7 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
         <v>1.73</v>
@@ -713,10 +713,10 @@
         <v>6.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AF2" t="n">
         <v>1.5</v>
@@ -1046,7 +1046,7 @@
         <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1055,7 +1055,7 @@
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
         <v>2.51</v>
@@ -1079,7 +1079,7 @@
         <v>1.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
         <v>1.72</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.28</v>
       </c>
-      <c r="M13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>9</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.71</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.35</v>
+        <v>1.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>6.25</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.42</v>
+        <v>1.02</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.2</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>9.35</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.09</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.02</v>
+        <v>3.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.54</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.71</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>4.59</v>
+        <v>2.53</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z29" t="n">
         <v>3.18</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V29" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.72</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
         <v>2.05</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O30" t="n">
-        <v>2.62</v>
+        <v>4.59</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AF30" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3.54</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.7</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.58</v>
+        <v>3.92</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
         <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
         <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>3.71</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>3.71</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
         <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,37 +5895,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="P46" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.78</v>
+        <v>5.85</v>
       </c>
       <c r="R46" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T46" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U46" t="n">
         <v>1.28</v>
       </c>
       <c r="V46" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W46" t="n">
         <v>1.01</v>
@@ -5940,28 +5940,28 @@
         <v>2.83</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
         <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD46" t="n">
         <v>1.18</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -668,19 +668,19 @@
         <v>2.51</v>
       </c>
       <c r="O2" t="n">
-        <v>3.76</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
         <v>4.25</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="P5" t="n">
         <v>1.88</v>
@@ -1034,10 +1034,10 @@
         <v>4.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
         <v>3.52</v>
@@ -1049,7 +1049,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>1.71</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>9.35</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.09</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.02</v>
+        <v>3.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>10.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>4.42</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>4.42</v>
       </c>
       <c r="O15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.35</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2</v>
+        <v>5.85</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>5.85</v>
+        <v>7.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>3.8</v>
+        <v>4.59</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.54</v>
+        <v>2.72</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.53</v>
+        <v>3.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.71</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.2</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="AA30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.28</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.54</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>3.71</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.08</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V34" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
         <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,61 +4586,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N35" t="n">
-        <v>3.71</v>
+        <v>4.08</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
         <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE35" t="n">
         <v>1.83</v>
@@ -4649,7 +4649,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
         <v>1.73</v>
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="N36" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
         <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="R36" t="n">
         <v>1.28</v>
@@ -4741,13 +4741,13 @@
         <v>1.09</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="AA36" t="n">
         <v>1.6</v>
@@ -4762,16 +4762,16 @@
         <v>1.46</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
         <v>2.44</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46090.64583333334</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>2.79</v>
+        <v>3.68</v>
       </c>
       <c r="T37" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>5.45</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>3.68</v>
+        <v>2.79</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="U38" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.11</v>
+        <v>3.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M48" t="n">
         <v>3.25</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.22</v>
-      </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>4.18</v>
+        <v>2.96</v>
       </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.79</v>
+        <v>4.34</v>
       </c>
       <c r="R48" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="S48" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="T48" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U48" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
         <v>1.03</v>
       </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y48" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N49" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O49" t="n">
-        <v>2.8</v>
+        <v>4.18</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.72</v>
+        <v>2.79</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S49" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="U49" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
         <v>1.02</v>
       </c>
-      <c r="X49" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y49" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.65</v>
+        <v>3.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46090.83333333334</v>
@@ -7094,64 +7094,64 @@
         <v>5.34</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46090.89583333334</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.38</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1992,10 +1992,10 @@
         <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
         <v>6.25</v>
@@ -2007,10 +2007,10 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="AA13" t="n">
         <v>1.72</v>
@@ -2028,7 +2028,7 @@
         <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
         <v>1.09</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>2.38</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>3.02</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>3.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.16</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="U14" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>5.3</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.52</v>
+        <v>3.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.91</v>
+        <v>3.76</v>
       </c>
       <c r="N15" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>2.93</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.24</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.39</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.31</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V24" t="n">
-        <v>5.85</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.35</v>
+        <v>2.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.13</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.75</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.54</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,61 +4348,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N33" t="n">
-        <v>3.71</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.33</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
         <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
         <v>1.83</v>
@@ -4411,7 +4411,7 @@
         <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
         <v>1.73</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,70 +4586,70 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="O35" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
         <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.55</v>
+        <v>3.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
         <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
         <v>1.73</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="O37" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.15</v>
+        <v>5.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>3.68</v>
+        <v>2.79</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="U37" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.11</v>
+        <v>3.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>2.79</v>
+        <v>3.68</v>
       </c>
       <c r="T38" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="V38" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>4.53</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>6.23</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="U42" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
         <v>3.22</v>
       </c>
       <c r="N49" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>4.18</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.79</v>
+        <v>4.34</v>
       </c>
       <c r="R49" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V49" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X49" t="n">
         <v>1.03</v>
       </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M50" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V50" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z50" t="n">
         <v>3.08</v>
       </c>
-      <c r="N50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V50" t="n">
-        <v>7</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.86</v>
-      </c>
       <c r="AA50" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -665,10 +665,10 @@
         <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="P2" t="n">
         <v>1.72</v>
@@ -701,7 +701,7 @@
         <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="n">
         <v>3.05</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1031,13 +1031,13 @@
         <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="T5" t="n">
         <v>3.52</v>
@@ -1049,7 +1049,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
@@ -1070,7 +1070,7 @@
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
         <v>2.14</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="O8" t="n">
         <v>4.2</v>
@@ -1388,7 +1388,7 @@
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
         <v>1.48</v>
@@ -1400,16 +1400,16 @@
         <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.35</v>
@@ -1418,25 +1418,25 @@
         <v>2.72</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
         <v>1.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.94</v>
+        <v>4.17</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
         <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
         <v>1.33</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1861,25 +1861,25 @@
         <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.09</v>
@@ -1891,31 +1891,31 @@
         <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -2209,7 +2209,7 @@
         <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="N15" t="n">
         <v>4.3</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
         <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>4.08</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
         <v>2.09</v>
@@ -2599,7 +2599,7 @@
         <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
         <v>1.36</v>
@@ -2611,13 +2611,13 @@
         <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
         <v>1.98</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.36</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>2.93</v>
+        <v>4.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.31</v>
       </c>
-      <c r="V24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>3.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>7.16</v>
       </c>
       <c r="O25" t="n">
         <v>1.88</v>
@@ -3450,7 +3450,7 @@
         <v>2.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
         <v>1.88</v>
@@ -3459,10 +3459,10 @@
         <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3759,7 +3759,7 @@
         <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O28" t="n">
         <v>4.59</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.83</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="P30" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
         <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="O31" t="n">
         <v>2.53</v>
@@ -4128,10 +4128,10 @@
         <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T31" t="n">
         <v>2.95</v>
@@ -4140,16 +4140,16 @@
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
         <v>3.18</v>
@@ -4158,13 +4158,13 @@
         <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE31" t="n">
         <v>1.84</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.01</v>
       </c>
       <c r="O32" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.92</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
         <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="T32" t="n">
         <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
         <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.25</v>
+        <v>4.77</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
         <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
         <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AA33" t="n">
         <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="U34" t="n">
         <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
         <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="T35" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>4.75</v>
+        <v>3.12</v>
       </c>
       <c r="O37" t="n">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="P37" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>2.79</v>
+        <v>3.68</v>
       </c>
       <c r="T37" t="n">
-        <v>2.67</v>
+        <v>2.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V37" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>5.67</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S38" t="n">
-        <v>3.68</v>
+        <v>2.71</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="U38" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="M39" t="n">
-        <v>4.53</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>6.23</v>
+        <v>1.86</v>
       </c>
       <c r="O39" t="n">
-        <v>2.01</v>
+        <v>5.32</v>
       </c>
       <c r="P39" t="n">
-        <v>2.51</v>
+        <v>2.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.65</v>
+        <v>2.39</v>
       </c>
       <c r="R39" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="V39" t="n">
-        <v>5.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.61</v>
+        <v>4.15</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,40 +5300,40 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>1.86</v>
+        <v>5.2</v>
       </c>
       <c r="O41" t="n">
-        <v>5.32</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.39</v>
+        <v>7.04</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T41" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U41" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V41" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
         <v>1.04</v>
@@ -5345,28 +5345,28 @@
         <v>2.59</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.11</v>
+        <v>2.11</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5904,13 +5904,13 @@
         <v>1.53</v>
       </c>
       <c r="O46" t="n">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="P46" t="n">
         <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R46" t="n">
         <v>1.49</v>
@@ -5955,7 +5955,7 @@
         <v>2.32</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
         <v>1.22</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="M47" t="n">
         <v>3.08</v>
@@ -6050,7 +6050,7 @@
         <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y47" t="n">
         <v>1.38</v>
@@ -6059,16 +6059,16 @@
         <v>2.62</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AB47" t="n">
         <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE47" t="n">
         <v>1.98</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA49" t="n">
         <v>2.05</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V49" t="n">
-        <v>7</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG49" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC49" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
         <v>3.22</v>
       </c>
       <c r="N50" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>4.18</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.79</v>
+        <v>4.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V50" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X50" t="n">
         <v>1.03</v>
       </c>
-      <c r="X50" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y50" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,25 +6490,25 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O51" t="n">
         <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="R51" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S51" t="n">
         <v>2.6</v>
@@ -6526,7 +6526,7 @@
         <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
         <v>1.36</v>
@@ -6535,10 +6535,10 @@
         <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC51" t="n">
         <v>3.74</v>
@@ -6547,7 +6547,7 @@
         <v>1.22</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF51" t="n">
         <v>1.8</v>
@@ -6609,28 +6609,28 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="P52" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q52" t="n">
         <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T52" t="n">
         <v>2.75</v>
@@ -6651,7 +6651,7 @@
         <v>1.28</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA52" t="n">
         <v>2.1</v>
@@ -6660,22 +6660,22 @@
         <v>1.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AD52" t="n">
         <v>1.23</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46090.71875</v>
@@ -7088,10 +7088,10 @@
         <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="N56" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="O56" t="n">
         <v>2.18</v>
@@ -7133,13 +7133,13 @@
         <v>1.86</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC56" t="n">
         <v>3.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE56" t="n">
         <v>1.97</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
         <v>4.45</v>
@@ -677,10 +677,10 @@
         <v>3.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="T2" t="n">
         <v>4.25</v>
@@ -701,7 +701,7 @@
         <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AA2" t="n">
         <v>3.05</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>1.96</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>3.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.5</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.2</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.35</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.38</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.81</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.02</v>
+        <v>1.71</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.59</v>
+        <v>9.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>3.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.71</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>4.72</v>
       </c>
       <c r="O18" t="n">
         <v>2.41</v>
@@ -2602,7 +2602,7 @@
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
         <v>2.7</v>
@@ -3280,31 +3280,31 @@
         <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>7</v>
@@ -3313,37 +3313,37 @@
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="AA24" t="n">
         <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
         <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG24" t="n">
         <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>4.16</v>
       </c>
       <c r="O30" t="n">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.54</v>
+        <v>4.7</v>
       </c>
       <c r="R30" t="n">
         <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
         <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>6.65</v>
       </c>
       <c r="W30" t="n">
         <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
         <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z31" t="n">
         <v>3.54</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.94</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="P32" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
         <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,43 +5062,43 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
-        <v>5.32</v>
+        <v>7.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
         <v>1.39</v>
@@ -5107,28 +5107,28 @@
         <v>2.59</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD39" t="n">
         <v>1.16</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="O40" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF40" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q40" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="P45" t="n">
-        <v>2.51</v>
+        <v>1.94</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="T45" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="U45" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.98</v>
+        <v>2.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,43 +5895,43 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>7.4</v>
+        <v>5.32</v>
       </c>
       <c r="P46" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="R46" t="n">
         <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U46" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V46" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
         <v>1.39</v>
@@ -5940,28 +5940,28 @@
         <v>2.59</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD46" t="n">
         <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,16 +6133,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
         <v>2.05</v>
@@ -6151,22 +6151,22 @@
         <v>4.34</v>
       </c>
       <c r="R48" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
         <v>3.3</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V48" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
         <v>1.03</v>
@@ -6175,31 +6175,31 @@
         <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O50" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="P50" t="n">
         <v>2.05</v>
@@ -6389,22 +6389,22 @@
         <v>4.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
         <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
         <v>1.03</v>
@@ -6413,31 +6413,31 @@
         <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -662,67 +662,67 @@
         <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.68</v>
+        <v>2.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AH2" t="n">
         <v>1.31</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="O4" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.51</v>
+        <v>2.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>5.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>3.21</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.81</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>1.71</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.59</v>
+        <v>9.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.67</v>
+        <v>3.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>3.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>3.21</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N14" t="n">
         <v>1.28</v>
       </c>
-      <c r="M14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>9</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.71</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.35</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="U14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.42</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.2</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>3.71</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
         <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC24" t="n">
         <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.79</v>
+        <v>3.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
         <v>1.34</v>
@@ -3658,13 +3658,13 @@
         <v>3.11</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
         <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
         <v>1.08</v>
@@ -3673,34 +3673,34 @@
         <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>4.59</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>4.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>3.71</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
-        <v>2.97</v>
+        <v>4.59</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>6.45</v>
+        <v>8.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.05</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4351,70 +4351,70 @@
         <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
         <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4470,70 +4470,70 @@
         <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.4</v>
+        <v>4.77</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.33</v>
       </c>
-      <c r="V34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z34" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4714,7 +4714,7 @@
         <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="P36" t="n">
         <v>2.26</v>
@@ -4729,7 +4729,7 @@
         <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
         <v>1.53</v>
@@ -4744,10 +4744,10 @@
         <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="AA36" t="n">
         <v>1.6</v>
@@ -4756,19 +4756,19 @@
         <v>2.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE36" t="n">
         <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.38</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,22 +5062,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.75</v>
+        <v>3.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>7.4</v>
+        <v>4.33</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
@@ -5092,19 +5092,19 @@
         <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA39" t="n">
         <v>2.27</v>
@@ -5113,22 +5113,22 @@
         <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.96</v>
+        <v>6.52</v>
       </c>
       <c r="M47" t="n">
-        <v>3.08</v>
+        <v>3.52</v>
       </c>
       <c r="N47" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="O47" t="n">
-        <v>4.97</v>
+        <v>7</v>
       </c>
       <c r="P47" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="R47" t="n">
         <v>1.49</v>
@@ -6044,43 +6044,43 @@
         <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="O50" t="n">
         <v>2.96</v>
@@ -6389,16 +6389,16 @@
         <v>4.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T50" t="n">
         <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
         <v>9.1</v>
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y50" t="n">
         <v>1.36</v>
@@ -6416,10 +6416,10 @@
         <v>2.72</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC50" t="n">
         <v>4.1</v>
@@ -6434,10 +6434,10 @@
         <v>1.79</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6850,10 +6850,10 @@
         <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N54" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>2.04</v>
@@ -6907,13 +6907,13 @@
         <v>2.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG54" t="n">
         <v>1.21</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46090.83333333334</v>
@@ -7088,10 +7088,10 @@
         <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="O56" t="n">
         <v>2.18</v>
@@ -7112,7 +7112,7 @@
         <v>2.96</v>
       </c>
       <c r="U56" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V56" t="n">
         <v>7.9</v>
@@ -7124,10 +7124,10 @@
         <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA56" t="n">
         <v>1.86</v>
@@ -7136,7 +7136,7 @@
         <v>1.73</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="AD56" t="n">
         <v>1.22</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="M2" t="n">
-        <v>2.76</v>
+        <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
@@ -677,13 +677,13 @@
         <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -710,10 +710,10 @@
         <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
         <v>2.22</v>
@@ -722,10 +722,10 @@
         <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N4" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
         <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
         <v>4.7</v>
@@ -933,7 +933,7 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
         <v>1.62</v>
@@ -960,7 +960,7 @@
         <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
         <v>1.69</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.28</v>
       </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>10</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.71</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.35</v>
+        <v>1.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.42</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.21</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>2.43</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
       </c>
-      <c r="O14" t="n">
-        <v>11</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.71</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="M17" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
         <v>4.72</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,22 +2721,22 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2745,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46090.47916666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.36</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
         <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.02</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.76</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>3.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>7.16</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
         <v>1.88</v>
@@ -3182,7 +3182,7 @@
         <v>3.32</v>
       </c>
       <c r="T23" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="U23" t="n">
         <v>1.5</v>
@@ -3194,7 +3194,7 @@
         <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>1.18</v>
@@ -3206,25 +3206,25 @@
         <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.26</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>2.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3524,13 +3524,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
@@ -3646,16 +3646,16 @@
         <v>3.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
         <v>2.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
         <v>2.55</v>
@@ -3670,25 +3670,25 @@
         <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.9</v>
+        <v>4.19</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC27" t="n">
         <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
         <v>1.56</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="O28" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.02</v>
+        <v>2.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="T28" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.54</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>3.37</v>
       </c>
       <c r="N30" t="n">
-        <v>4.16</v>
+        <v>3.31</v>
       </c>
       <c r="O30" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.7</v>
+        <v>4.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.18</v>
+        <v>3.79</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="P31" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.58</v>
+        <v>3.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>3.23</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.82</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.71</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>4.16</v>
       </c>
       <c r="O32" t="n">
-        <v>4.59</v>
+        <v>2.53</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC32" t="n">
         <v>3.18</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4</v>
-      </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,70 +4348,70 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>4.77</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
         <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.71</v>
+        <v>3.98</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
         <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
         <v>1.73</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4470,70 +4470,70 @@
         <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
         <v>1.92</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4586,61 +4586,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
         <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
         <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE35" t="n">
         <v>1.84</v>
@@ -4652,7 +4652,7 @@
         <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4824,40 +4824,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M37" t="n">
         <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
         <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="U37" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V37" t="n">
         <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
@@ -4869,25 +4869,25 @@
         <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AD37" t="n">
         <v>1.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH37" t="n">
         <v>1.7</v>
@@ -4946,31 +4946,31 @@
         <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.67</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="T38" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="U38" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
         <v>6.7</v>
@@ -4982,34 +4982,34 @@
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG38" t="n">
         <v>1.19</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="M39" t="n">
         <v>3</v>
@@ -5110,7 +5110,7 @@
         <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
         <v>4.23</v>
@@ -5119,10 +5119,10 @@
         <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
         <v>1.28</v>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
         <v>5.25</v>
@@ -5193,28 +5193,28 @@
         <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.65</v>
+        <v>4.57</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
         <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="U40" t="n">
         <v>1.48</v>
       </c>
       <c r="V40" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
         <v>1.01</v>
@@ -5223,16 +5223,16 @@
         <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AD40" t="n">
         <v>1.39</v>
@@ -5241,7 +5241,7 @@
         <v>1.77</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
         <v>1.22</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.52</v>
+        <v>6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N47" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O47" t="n">
         <v>7</v>
@@ -6053,10 +6053,10 @@
         <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA47" t="n">
         <v>2.2</v>
@@ -6133,55 +6133,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="O48" t="n">
         <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S48" t="n">
         <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U48" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W48" t="n">
         <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
         <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
         <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC48" t="n">
         <v>3.86</v>
@@ -6255,31 +6255,31 @@
         <v>3.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O49" t="n">
         <v>4.22</v>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U49" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V49" t="n">
         <v>7.3</v>
@@ -6297,7 +6297,7 @@
         <v>3.08</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB49" t="n">
         <v>1.75</v>
@@ -6309,13 +6309,13 @@
         <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF49" t="n">
         <v>1.95</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
         <v>1.29</v>
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
         <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="O50" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="P50" t="n">
         <v>2.05</v>
@@ -6389,16 +6389,16 @@
         <v>4.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
         <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
         <v>9.1</v>
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y50" t="n">
         <v>1.36</v>
@@ -6419,25 +6419,25 @@
         <v>2.27</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
         <v>4.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,25 +6490,25 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N51" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O51" t="n">
         <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S51" t="n">
         <v>2.6</v>
@@ -6520,28 +6520,28 @@
         <v>1.35</v>
       </c>
       <c r="V51" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
         <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y51" t="n">
         <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD51" t="n">
         <v>1.22</v>
@@ -6550,7 +6550,7 @@
         <v>1.95</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
         <v>1.3</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
         <v>2.69</v>
@@ -6624,37 +6624,37 @@
         <v>1.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S52" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="U52" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W52" t="n">
         <v>1.02</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
         <v>1.28</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB52" t="n">
         <v>1.8</v>
@@ -6666,10 +6666,10 @@
         <v>1.23</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG52" t="n">
         <v>1.35</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="M2" t="n">
         <v>2.93</v>
@@ -677,13 +677,13 @@
         <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -710,10 +710,10 @@
         <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
         <v>2.22</v>
@@ -722,10 +722,10 @@
         <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
         <v>5.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>5.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="O14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>2.43</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>8.800000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.27</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.42</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>9.800000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.29</v>
       </c>
-      <c r="Q22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>2.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.14</v>
+        <v>4.25</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.87</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.15</v>
+        <v>7.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.15</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>3.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.33</v>
+        <v>2.94</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="AG28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>2.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3.31</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.58</v>
+        <v>4.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
         <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>3.31</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.62</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>4.16</v>
       </c>
       <c r="O31" t="n">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>6.45</v>
+        <v>6.65</v>
       </c>
       <c r="W31" t="n">
         <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.91</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
+      <c r="AF32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,70 +4348,70 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
         <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.98</v>
+        <v>3.71</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
         <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
         <v>1.73</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,70 +4467,70 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>4.77</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
         <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>3.98</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE34" t="n">
         <v>1.92</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
         <v>1.73</v>
@@ -4744,10 +4744,10 @@
         <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="AA36" t="n">
         <v>1.6</v>
@@ -4756,7 +4756,7 @@
         <v>2.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AD36" t="n">
         <v>1.52</v>
@@ -6847,25 +6847,25 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N54" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O54" t="n">
         <v>2.04</v>
       </c>
       <c r="P54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
         <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S54" t="n">
         <v>2.77</v>
@@ -6883,28 +6883,28 @@
         <v>1.05</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>3.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
         <v>1.7</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -683,7 +683,7 @@
         <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -698,10 +698,10 @@
         <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AA2" t="n">
         <v>2.66</v>
@@ -710,7 +710,7 @@
         <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.09</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46090.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>2.43</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.28</v>
       </c>
-      <c r="O12" t="n">
-        <v>11</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.2</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.82</v>
       </c>
       <c r="O13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.71</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.82</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.43</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>9.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>3.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA24" t="n">
         <v>1.75</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.82</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.85</v>
+        <v>3.82</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>2.17</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC27" t="n">
         <v>3.35</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="T28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.59</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AA28" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>4.16</v>
       </c>
       <c r="O30" t="n">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U30" t="n">
         <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>6.65</v>
       </c>
       <c r="W30" t="n">
         <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
         <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC30" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>4.16</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="P31" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
         <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="W31" t="n">
         <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
         <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.33</v>
+        <v>2.94</v>
       </c>
       <c r="T32" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
         <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.71</v>
+        <v>3.94</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,70 +4467,70 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
         <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.98</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
         <v>1.92</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
         <v>1.73</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.38</v>
+        <v>4.77</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
         <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4729,7 +4729,7 @@
         <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U36" t="n">
         <v>1.53</v>
@@ -4744,10 +4744,10 @@
         <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="AA36" t="n">
         <v>1.6</v>
@@ -4759,13 +4759,13 @@
         <v>2.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE36" t="n">
         <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AG36" t="n">
         <v>1.25</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="U37" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O38" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V38" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z38" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH38" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,22 +5062,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
@@ -5092,43 +5092,43 @@
         <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA39" t="n">
         <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.5</v>
       </c>
-      <c r="M40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="T40" t="n">
-        <v>2.57</v>
+        <v>3.34</v>
       </c>
       <c r="U40" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>5.75</v>
+        <v>8.9</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,34 +5895,34 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O46" t="n">
-        <v>5.32</v>
+        <v>4.33</v>
       </c>
       <c r="P46" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="R46" t="n">
         <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T46" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V46" t="n">
         <v>8.699999999999999</v>
@@ -5934,34 +5934,34 @@
         <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD46" t="n">
         <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="O48" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2.7</v>
       </c>
-      <c r="P48" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R48" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T48" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
         <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="O49" t="n">
-        <v>4.22</v>
+        <v>2.96</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.7</v>
+        <v>4.08</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S49" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="T49" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V49" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M50" t="n">
         <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2.87</v>
+        <v>3.58</v>
       </c>
       <c r="O50" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
         <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
         <v>3.85</v>
@@ -6865,7 +6865,7 @@
         <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
         <v>2.77</v>
@@ -6895,16 +6895,16 @@
         <v>1.97</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC54" t="n">
         <v>3.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF54" t="n">
         <v>1.7</v>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
         <v>4.6</v>
@@ -7109,7 +7109,7 @@
         <v>2.66</v>
       </c>
       <c r="T56" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U56" t="n">
         <v>1.32</v>
@@ -7124,25 +7124,25 @@
         <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AB56" t="n">
         <v>1.73</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AD56" t="n">
         <v>1.22</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF56" t="n">
         <v>1.73</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
@@ -695,7 +695,7 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
         <v>1.63</v>
@@ -704,7 +704,7 @@
         <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AB2" t="n">
         <v>1.37</v>
@@ -722,10 +722,10 @@
         <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46090.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.43</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>3.05</v>
+        <v>1.72</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>3.82</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>2.43</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>6.79</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
         <v>1.58</v>
@@ -3081,31 +3081,31 @@
         <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
         <v>4.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
         <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
         <v>7</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2.49</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
         <v>3.5</v>
@@ -3524,13 +3524,13 @@
         <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3.35</v>
+        <v>3.79</v>
       </c>
       <c r="P26" t="n">
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
@@ -3539,31 +3539,31 @@
         <v>2.91</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U26" t="n">
         <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
         <v>1.69</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AC26" t="n">
         <v>2.75</v>
@@ -3575,7 +3575,7 @@
         <v>1.56</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG26" t="n">
         <v>1.25</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
         <v>2.85</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC28" t="n">
         <v>3.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.07</v>
+        <v>3.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.37</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>3.31</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.02</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.91</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AF30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4119,7 +4119,7 @@
         <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
@@ -4137,7 +4137,7 @@
         <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
         <v>6.45</v>
@@ -4146,19 +4146,19 @@
         <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
         <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
         <v>3.05</v>
@@ -4167,10 +4167,10 @@
         <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
         <v>1.28</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.58</v>
+        <v>4.03</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
         <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>3.84</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.38</v>
+        <v>4.77</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="T33" t="n">
         <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
         <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>2.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
         <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA34" t="n">
         <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,70 +4586,70 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
         <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
         <v>1.73</v>
@@ -4824,22 +4824,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="P37" t="n">
         <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.1</v>
+        <v>5.34</v>
       </c>
       <c r="R37" t="n">
         <v>1.34</v>
@@ -4869,13 +4869,13 @@
         <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
         <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AD37" t="n">
         <v>1.28</v>
@@ -4887,10 +4887,10 @@
         <v>1.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
         <v>2.9</v>
@@ -4961,16 +4961,16 @@
         <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
         <v>4.4</v>
@@ -4994,7 +4994,7 @@
         <v>2.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AD38" t="n">
         <v>1.7</v>
@@ -5003,7 +5003,7 @@
         <v>1.38</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AG38" t="n">
         <v>1.24</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.75</v>
+        <v>1.46</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF39" t="n">
         <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.53</v>
       </c>
       <c r="AG39" t="n">
         <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.04</v>
+        <v>5.53</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="T40" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="V40" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH40" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="AF41" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.59</v>
+        <v>3.82</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="T42" t="n">
-        <v>3.12</v>
+        <v>2.56</v>
       </c>
       <c r="U42" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="V42" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="W42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X42" t="n">
         <v>1.01</v>
       </c>
-      <c r="X42" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z42" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="AE42" t="n">
         <v>1.63</v>
       </c>
-      <c r="AC42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5538,19 +5538,19 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O43" t="n">
-        <v>5.32</v>
+        <v>5.6</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
         <v>2.39</v>
@@ -5562,13 +5562,13 @@
         <v>2.34</v>
       </c>
       <c r="T43" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V43" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W43" t="n">
         <v>1.01</v>
@@ -5577,19 +5577,19 @@
         <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD43" t="n">
         <v>1.16</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.67</v>
+        <v>6.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U46" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V46" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
         <v>1.01</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y46" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.18</v>
+        <v>2.23</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N48" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>4.22</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1.4</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="Z48" t="n">
         <v>2.8</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AA48" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N50" t="n">
         <v>2.2</v>
       </c>
-      <c r="M50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.58</v>
-      </c>
       <c r="O50" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q50" t="n">
         <v>2.7</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S50" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T50" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V50" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,55 +6490,55 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="M51" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
         <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
         <v>4.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S51" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U51" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V51" t="n">
         <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
         <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AA51" t="n">
         <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
         <v>4</v>
@@ -6609,16 +6609,16 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="M52" t="n">
         <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="P52" t="n">
         <v>1.99</v>
@@ -6627,16 +6627,16 @@
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
         <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="U52" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V52" t="n">
         <v>7.9</v>
@@ -6645,7 +6645,7 @@
         <v>1.02</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
         <v>1.28</v>
@@ -6657,10 +6657,10 @@
         <v>2.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="AD52" t="n">
         <v>1.23</v>
@@ -6675,7 +6675,7 @@
         <v>1.35</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46090.71875</v>
@@ -6687,27 +6687,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46090.75</v>
+        <v>46090.72916666666</v>
       </c>
     </row>
     <row r="54">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,76 +6847,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46090.83333333334</v>
+        <v>46090.75</v>
       </c>
     </row>
     <row r="55">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,76 +6966,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>46090.85416666666</v>
+        <v>46090.83333333334</v>
       </c>
     </row>
     <row r="56">
@@ -7044,116 +7044,235 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
+        <v>46090.85416666666</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="L57" t="n">
         <v>1.61</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M57" t="n">
         <v>3.5</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N57" t="n">
         <v>4.6</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O57" t="n">
         <v>2.18</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P57" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q57" t="n">
         <v>5</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R57" t="n">
         <v>1.39</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S57" t="n">
         <v>2.66</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U56" t="n">
+      <c r="T57" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.32</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V57" t="n">
         <v>7.9</v>
       </c>
-      <c r="W56" t="n">
+      <c r="W57" t="n">
         <v>1.02</v>
       </c>
-      <c r="X56" t="n">
+      <c r="X57" t="n">
         <v>1</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y57" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z57" t="n">
         <v>3.05</v>
       </c>
-      <c r="AA56" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="AA57" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF57" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG56" t="n">
+      <c r="AG57" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH57" t="n">
         <v>2.16</v>
       </c>
-      <c r="AI56" s="3" t="n">
+      <c r="AI57" s="3" t="n">
         <v>46090.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
@@ -677,10 +677,10 @@
         <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="T2" t="n">
         <v>3.82</v>
@@ -695,16 +695,16 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z2" t="n">
         <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AB2" t="n">
         <v>1.37</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.9</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.220000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.42</v>
       </c>
-      <c r="V12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
         <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2331,13 +2331,13 @@
         <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>4.08</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
         <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
         <v>4.85</v>
@@ -2349,10 +2349,10 @@
         <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
         <v>8.4</v>
@@ -2370,7 +2370,7 @@
         <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB16" t="n">
         <v>1.64</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.25</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC22" t="n">
-        <v>4.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="N25" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.32</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>2.49</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.91</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.62</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.58</v>
+        <v>4.03</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.8</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,37 +4110,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.69</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.45</v>
+        <v>6.65</v>
       </c>
       <c r="W31" t="n">
         <v>1.05</v>
@@ -4149,34 +4149,34 @@
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2.05</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.77</v>
+        <v>3.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.32</v>
       </c>
-      <c r="V33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z33" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
         <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>4.77</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>5.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>5.3</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P39" t="n">
         <v>2</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.33</v>
-      </c>
       <c r="Q39" t="n">
-        <v>4.57</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="T39" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.61</v>
+        <v>4.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG39" t="n">
         <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
-        <v>4.33</v>
+        <v>2.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.67</v>
+        <v>5.08</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S41" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.27</v>
       </c>
-      <c r="V41" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O42" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.82</v>
+        <v>6.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S42" t="n">
-        <v>2.92</v>
+        <v>2.53</v>
       </c>
       <c r="T42" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="U42" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>5.95</v>
+        <v>8.1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X42" t="n">
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,37 +5538,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="R43" t="n">
         <v>1.49</v>
       </c>
       <c r="S43" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
         <v>1.27</v>
       </c>
       <c r="V43" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W43" t="n">
         <v>1.01</v>
@@ -5586,7 +5586,7 @@
         <v>2.27</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC43" t="n">
         <v>4.1</v>
@@ -5595,16 +5595,16 @@
         <v>1.16</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.08</v>
+        <v>5.53</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U44" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V44" t="n">
-        <v>6.85</v>
+        <v>8.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA44" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH44" t="n">
         <v>1.89</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.75</v>
+        <v>1.46</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V45" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.53</v>
       </c>
       <c r="AG45" t="n">
         <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.9</v>
+        <v>3.82</v>
       </c>
       <c r="R46" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S46" t="n">
-        <v>2.53</v>
+        <v>2.92</v>
       </c>
       <c r="T46" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="U46" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>8.1</v>
+        <v>5.95</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="P48" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="R48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.5</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC48" t="n">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.08</v>
+        <v>4.33</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>2.43</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>5.35</v>
+        <v>6.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.43</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>5.03</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
@@ -2248,25 +2248,25 @@
         <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD15" t="n">
         <v>1.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
         <v>1.1</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
         <v>2.33</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.25</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC23" t="n">
-        <v>4.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>2.27</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.79</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>3.79</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O28" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.8</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.03</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.62</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>4.03</v>
       </c>
       <c r="R30" t="n">
         <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE30" t="n">
+      <c r="AH30" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,37 +4110,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="P31" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.7</v>
+        <v>3.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="W31" t="n">
         <v>1.05</v>
@@ -4149,34 +4149,34 @@
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.25</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
       <c r="O33" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4467,16 +4467,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="P34" t="n">
         <v>2.1</v>
@@ -4485,7 +4485,7 @@
         <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
         <v>2.62</v>
@@ -4506,7 +4506,7 @@
         <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
         <v>3</v>
@@ -4518,7 +4518,7 @@
         <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="AD34" t="n">
         <v>1.25</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.77</v>
+        <v>3.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.32</v>
       </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4714,7 +4714,7 @@
         <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
         <v>2.26</v>
@@ -4729,7 +4729,7 @@
         <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U36" t="n">
         <v>1.53</v>
@@ -4756,13 +4756,13 @@
         <v>2.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AD36" t="n">
         <v>1.46</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF36" t="n">
         <v>2.44</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.34</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>2.83</v>
+        <v>3.68</v>
       </c>
       <c r="T37" t="n">
-        <v>2.67</v>
+        <v>2.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V37" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z37" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>5.34</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.68</v>
+        <v>2.83</v>
       </c>
       <c r="T38" t="n">
-        <v>2.11</v>
+        <v>2.67</v>
       </c>
       <c r="U38" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.75</v>
+        <v>1.46</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF39" t="n">
         <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.53</v>
       </c>
       <c r="AG39" t="n">
         <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O41" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.08</v>
+        <v>6.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S41" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V41" t="n">
-        <v>6.85</v>
+        <v>8.1</v>
       </c>
       <c r="W41" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.9</v>
+        <v>5.08</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S42" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="T42" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>8.1</v>
+        <v>6.85</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="P45" t="n">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.57</v>
+        <v>5.53</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="T45" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="U45" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.61</v>
+        <v>3.82</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.61</v>
+        <v>5.6</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.82</v>
+        <v>2.39</v>
       </c>
       <c r="R46" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="T46" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="V46" t="n">
-        <v>5.95</v>
+        <v>8.6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,55 +6014,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="P47" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="R47" t="n">
         <v>1.49</v>
       </c>
       <c r="S47" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
         <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA47" t="n">
         <v>2.27</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
         <v>4.1</v>
@@ -6071,16 +6071,16 @@
         <v>1.16</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>3.46</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O48" t="n">
-        <v>2.96</v>
+        <v>4.28</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.08</v>
+        <v>2.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S48" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC48" t="n">
         <v>3.3</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V48" t="n">
-        <v>9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="O49" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="P49" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="R49" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V49" t="n">
+        <v>9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB49" t="n">
         <v>1.5</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V49" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC49" t="n">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.46</v>
+        <v>2.14</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N50" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>4.28</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="U50" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="W50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X50" t="n">
         <v>1.03</v>
       </c>
-      <c r="X50" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y50" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -668,7 +668,7 @@
         <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.79</v>
@@ -677,13 +677,13 @@
         <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -698,19 +698,19 @@
         <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
         <v>2.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.3</v>
+        <v>5.74</v>
       </c>
       <c r="AD2" t="n">
         <v>1.09</v>
@@ -722,10 +722,10 @@
         <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.07</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.43</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>11.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.76</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="P23" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.95</v>
+        <v>9.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.32</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>5.95</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.28</v>
+        <v>4.24</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.49</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.27</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.95</v>
+        <v>2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.79</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.58</v>
+        <v>3.69</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.23</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
         <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="O29" t="n">
         <v>2.53</v>
@@ -3917,13 +3917,13 @@
         <v>3.18</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB29" t="n">
         <v>1.88</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AD29" t="n">
         <v>1.27</v>
@@ -4000,13 +4000,13 @@
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="R30" t="n">
         <v>1.34</v>
@@ -4015,7 +4015,7 @@
         <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
         <v>1.43</v>
@@ -4039,13 +4039,13 @@
         <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE30" t="n">
         <v>1.64</v>
@@ -4057,7 +4057,7 @@
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
-        <v>2.99</v>
+        <v>4.59</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.69</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V31" t="n">
-        <v>6.45</v>
+        <v>8.1</v>
       </c>
       <c r="W31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.05</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC32" t="n">
         <v>2.8</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD32" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4348,37 +4348,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>2.61</v>
       </c>
       <c r="P33" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
         <v>4.77</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.03</v>
@@ -4387,10 +4387,10 @@
         <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="AA33" t="n">
         <v>2.02</v>
@@ -4399,16 +4399,16 @@
         <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
         <v>1.29</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z35" t="n">
         <v>3</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF35" t="n">
         <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.57</v>
+        <v>2.67</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="T39" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>5.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AA39" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
-      </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3.82</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.9</v>
+        <v>3.82</v>
       </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>2.53</v>
+        <v>2.92</v>
       </c>
       <c r="T41" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="U41" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V41" t="n">
-        <v>8.1</v>
+        <v>5.95</v>
       </c>
       <c r="W41" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.75</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V42" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
         <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,37 +5538,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O43" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="R43" t="n">
         <v>1.49</v>
       </c>
       <c r="S43" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
         <v>1.27</v>
       </c>
       <c r="V43" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W43" t="n">
         <v>1.01</v>
@@ -5586,7 +5586,7 @@
         <v>2.27</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC43" t="n">
         <v>4.1</v>
@@ -5595,16 +5595,16 @@
         <v>1.16</v>
       </c>
       <c r="AE43" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.52</v>
+        <v>5.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>6.2</v>
+        <v>1.53</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.8</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V45" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC45" t="n">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="O46" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5.75</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="R47" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U47" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V47" t="n">
         <v>8.1</v>
@@ -6050,37 +6050,37 @@
         <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.05</v>
+        <v>2.23</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.46</v>
+        <v>2.82</v>
       </c>
       <c r="M48" t="n">
         <v>3.3</v>
@@ -6145,10 +6145,10 @@
         <v>4.28</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R48" t="n">
         <v>1.43</v>
@@ -6178,10 +6178,10 @@
         <v>3.08</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
         <v>3.3</v>
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="T49" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V49" t="n">
         <v>9</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6371,22 +6371,22 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="R50" t="n">
         <v>1.5</v>
@@ -6401,16 +6401,16 @@
         <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
         <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
         <v>2.8</v>
@@ -6422,22 +6422,22 @@
         <v>1.62</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD50" t="n">
         <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N51" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O51" t="n">
         <v>2.5</v>
@@ -6505,13 +6505,13 @@
         <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="T51" t="n">
         <v>3.24</v>
@@ -6520,13 +6520,13 @@
         <v>1.34</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X51" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
         <v>1.36</v>
@@ -6550,7 +6550,7 @@
         <v>1.95</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
         <v>1.3</v>
@@ -6966,22 +6966,22 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M55" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
         <v>2.04</v>
       </c>
       <c r="P55" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>5.13</v>
       </c>
       <c r="R55" t="n">
         <v>1.38</v>
@@ -7002,28 +7002,28 @@
         <v>1.05</v>
       </c>
       <c r="X55" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z55" t="n">
         <v>3.14</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB55" t="n">
         <v>1.82</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="AD55" t="n">
         <v>1.26</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AF55" t="n">
         <v>1.7</v>
@@ -7222,22 +7222,22 @@
         <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S57" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="T57" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V57" t="n">
         <v>7.9</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
         <v>1</v>
@@ -7249,13 +7249,13 @@
         <v>3.05</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="AD57" t="n">
         <v>1.22</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -713,7 +713,7 @@
         <v>5.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
         <v>2.22</v>
@@ -1022,13 +1022,13 @@
         <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
         <v>4.75</v>
@@ -1076,7 +1076,7 @@
         <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
         <v>1.39</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.73</v>
       </c>
       <c r="P11" t="n">
         <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
         <v>1.48</v>
@@ -1754,13 +1754,13 @@
         <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
         <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -1769,16 +1769,16 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
         <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
         <v>3.92</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.76</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.43</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.16</v>
+        <v>2.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>3.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>10.2</v>
       </c>
       <c r="M15" t="n">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>1.73</v>
+        <v>11.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.15</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6.35</v>
+        <v>5.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG15" t="n">
         <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2685,10 +2685,10 @@
         <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.64</v>
+        <v>2.81</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.42</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>2.27</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.78</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.27</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>4.59</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.69</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>6.45</v>
+        <v>8.1</v>
       </c>
       <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.05</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
         <v>3.5</v>
       </c>
-      <c r="N29" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.18</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.02</v>
+        <v>4.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.8</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V31" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="O32" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="P32" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.58</v>
+        <v>3.69</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>3.23</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.9</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.77</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
         <v>3</v>
@@ -4482,10 +4482,10 @@
         <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
         <v>2.69</v>
@@ -4497,7 +4497,7 @@
         <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
@@ -4506,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
         <v>2.88</v>
@@ -4515,16 +4515,16 @@
         <v>2.16</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD34" t="n">
         <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
         <v>1.86</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>4.77</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
         <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
         <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
         <v>3.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4827,19 +4827,19 @@
         <v>1.96</v>
       </c>
       <c r="M37" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q37" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.15</v>
       </c>
       <c r="R37" t="n">
         <v>1.21</v>
@@ -4854,10 +4854,10 @@
         <v>1.67</v>
       </c>
       <c r="V37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
@@ -4869,13 +4869,13 @@
         <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AD37" t="n">
         <v>1.7</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="M39" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC39" t="n">
         <v>3</v>
       </c>
-      <c r="N39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="AD39" t="n">
         <v>1.27</v>
       </c>
-      <c r="V39" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>2.23</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.53</v>
+        <v>4.61</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="T40" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="U40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
-        <v>2.61</v>
+        <v>4.33</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.82</v>
+        <v>2.67</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S41" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="T41" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="V41" t="n">
-        <v>5.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X41" t="n">
         <v>1.07</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.57</v>
+        <v>5.5</v>
       </c>
       <c r="R42" t="n">
         <v>1.31</v>
@@ -5449,19 +5449,19 @@
         <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W42" t="n">
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
         <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA42" t="n">
         <v>1.72</v>
@@ -5476,13 +5476,13 @@
         <v>1.39</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
         <v>2.5</v>
@@ -5538,22 +5538,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O43" t="n">
         <v>5.6</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="R43" t="n">
         <v>1.49</v>
@@ -5562,13 +5562,13 @@
         <v>2.34</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U43" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V43" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W43" t="n">
         <v>1.01</v>
@@ -5577,34 +5577,34 @@
         <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.1</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="U44" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="V44" t="n">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.59</v>
+        <v>3.28</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>6.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>2.33</v>
+        <v>6.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.08</v>
+        <v>2.11</v>
       </c>
       <c r="R45" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S45" t="n">
-        <v>2.71</v>
+        <v>2.52</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V45" t="n">
-        <v>6.85</v>
+        <v>9.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.14</v>
+        <v>4.29</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="N46" t="n">
-        <v>6.2</v>
+        <v>4.39</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S47" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T47" t="n">
         <v>2.97</v>
@@ -6044,25 +6044,25 @@
         <v>1.31</v>
       </c>
       <c r="V47" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>3.58</v>
@@ -6071,16 +6071,16 @@
         <v>1.21</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.82</v>
+        <v>2.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
-        <v>4.28</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.76</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V48" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.35</v>
       </c>
-      <c r="V48" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="O49" t="n">
-        <v>2.98</v>
+        <v>4.28</v>
       </c>
       <c r="P49" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.18</v>
+        <v>2.76</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="T49" t="n">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="U49" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
         <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.35</v>
+        <v>3.85</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S50" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T50" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V50" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
         <v>1.04</v>
       </c>
-      <c r="X50" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y50" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="M51" t="n">
         <v>3.35</v>
@@ -6502,7 +6502,7 @@
         <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
         <v>4.5</v>
@@ -6514,13 +6514,13 @@
         <v>2.6</v>
       </c>
       <c r="T51" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="U51" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V51" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W51" t="n">
         <v>1.04</v>
@@ -6529,16 +6529,16 @@
         <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
         <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC51" t="n">
         <v>4</v>
@@ -6553,10 +6553,10 @@
         <v>1.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46090.70833333334</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="M52" t="n">
         <v>3.05</v>
@@ -6621,22 +6621,22 @@
         <v>2.68</v>
       </c>
       <c r="P52" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R52" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
         <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="U52" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V52" t="n">
         <v>7.9</v>
@@ -6654,10 +6654,10 @@
         <v>3.08</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC52" t="n">
         <v>3.44</v>
@@ -6666,10 +6666,10 @@
         <v>1.23</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG52" t="n">
         <v>1.35</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>3.76</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.28</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>8</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
         <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.28</v>
       </c>
-      <c r="O15" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.49</v>
+        <v>2.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4.64</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.42</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.81</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AB23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.26</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>3.38</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3411,7 +3411,7 @@
         <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.31</v>
@@ -3420,19 +3420,19 @@
         <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="U25" t="n">
         <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.22</v>
@@ -3441,28 +3441,28 @@
         <v>4.24</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD25" t="n">
         <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.27</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>2.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.77</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>4.59</v>
+        <v>2.53</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.33</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.18</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.42</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.02</v>
+        <v>3.69</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>2.42</v>
       </c>
       <c r="P30" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.7</v>
+        <v>4.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4113,70 +4113,70 @@
         <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>3.23</v>
+        <v>2.33</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="O32" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.69</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.38</v>
       </c>
-      <c r="V32" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,61 +4348,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.3</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
         <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
         <v>1.8</v>
@@ -4411,10 +4411,10 @@
         <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,61 +4467,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
         <v>1.8</v>
@@ -4530,10 +4530,10 @@
         <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="M37" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="P37" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>5.24</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>3.68</v>
+        <v>2.92</v>
       </c>
       <c r="T37" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.59</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.7</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V38" t="n">
-        <v>6.7</v>
+        <v>4.33</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z38" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.55</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG39" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.23</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="P40" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.61</v>
+        <v>3.86</v>
       </c>
       <c r="R40" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="U40" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="M41" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC41" t="n">
         <v>3</v>
       </c>
-      <c r="N41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="AD41" t="n">
         <v>1.27</v>
       </c>
-      <c r="V41" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>2.23</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="O42" t="n">
-        <v>2.01</v>
+        <v>6.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="V42" t="n">
-        <v>5.75</v>
+        <v>9.5</v>
       </c>
       <c r="W42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X42" t="n">
         <v>1.08</v>
       </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y42" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.98</v>
+        <v>2.59</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.61</v>
+        <v>4.29</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N43" t="n">
-        <v>1.86</v>
+        <v>4.39</v>
       </c>
       <c r="O43" t="n">
-        <v>5.6</v>
+        <v>2.47</v>
       </c>
       <c r="P43" t="n">
         <v>1.89</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.49</v>
+        <v>5.66</v>
       </c>
       <c r="R43" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S43" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>3.28</v>
+        <v>2.76</v>
       </c>
       <c r="U43" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AB43" t="n">
         <v>1.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE43" t="n">
         <v>2.04</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG43" t="n">
         <v>1.27</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="P44" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>2.49</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S44" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="T44" t="n">
-        <v>2.67</v>
+        <v>3.28</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="V44" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>5.75</v>
       </c>
       <c r="O45" t="n">
-        <v>6.25</v>
+        <v>2.07</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.11</v>
+        <v>6.91</v>
       </c>
       <c r="R45" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S45" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U45" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V45" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF45" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC45" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AG45" t="n">
         <v>1.19</v>
       </c>
-      <c r="AE45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.05</v>
+        <v>2.39</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="M46" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>4.39</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="P46" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.66</v>
+        <v>4.61</v>
       </c>
       <c r="R46" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T46" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V46" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V47" t="n">
         <v>5.75</v>
       </c>
-      <c r="O47" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="W47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH47" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V47" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2.39</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N49" t="n">
         <v>3.25</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.15</v>
-      </c>
       <c r="O49" t="n">
-        <v>4.28</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S49" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
-        <v>2.94</v>
+        <v>3.56</v>
       </c>
       <c r="U49" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V49" t="n">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.38</v>
+        <v>4.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="O50" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.8</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.56</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="V50" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.6</v>
+        <v>3.37</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6621,22 +6621,22 @@
         <v>2.68</v>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
         <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="U52" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V52" t="n">
         <v>7.9</v>
@@ -6645,7 +6645,7 @@
         <v>1.02</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y52" t="n">
         <v>1.28</v>
@@ -6654,22 +6654,22 @@
         <v>3.08</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>3.44</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AG52" t="n">
         <v>1.35</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M55" t="n">
         <v>4</v>
@@ -6975,13 +6975,13 @@
         <v>6</v>
       </c>
       <c r="O55" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="P55" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.13</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
         <v>1.38</v>
@@ -6990,7 +6990,7 @@
         <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U55" t="n">
         <v>1.37</v>
@@ -7005,31 +7005,31 @@
         <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB55" t="n">
         <v>1.82</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AD55" t="n">
         <v>1.26</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH55" t="n">
         <v>2.49</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -665,16 +665,16 @@
         <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.64</v>
@@ -683,7 +683,7 @@
         <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -695,16 +695,16 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AB2" t="n">
         <v>1.4</v>
@@ -713,7 +713,7 @@
         <v>5.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
         <v>2.22</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46090.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>3.03</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.73</v>
+        <v>3.07</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10.2</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>8.5</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
         <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>10.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.76</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="O17" t="n">
         <v>2.41</v>
@@ -2465,13 +2465,13 @@
         <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
         <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
         <v>8.4</v>
@@ -2483,7 +2483,7 @@
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z17" t="n">
         <v>2.7</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.55</v>
+        <v>2.81</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>8.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.5</v>
       </c>
-      <c r="N28" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.18</v>
-      </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="O30" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.02</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4113,70 +4113,70 @@
         <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>9</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
         <v>3.5</v>
       </c>
       <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.03</v>
       </c>
-      <c r="O32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,34 +5062,34 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O39" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="P39" t="n">
         <v>1.89</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.67</v>
+        <v>2.49</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V39" t="n">
         <v>8.699999999999999</v>
@@ -5098,37 +5098,37 @@
         <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
         <v>1.55</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O40" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="P40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.58</v>
+        <v>2.39</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.55</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V41" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG41" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.23</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N42" t="n">
-        <v>1.55</v>
+        <v>5.51</v>
       </c>
       <c r="O42" t="n">
-        <v>6.25</v>
+        <v>2.14</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.11</v>
+        <v>6.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S42" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U42" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="W42" t="n">
         <v>1.02</v>
       </c>
       <c r="X42" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.29</v>
+        <v>3</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.38</v>
+        <v>1.21</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.05</v>
+        <v>2.23</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>4.39</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="P43" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.66</v>
+        <v>4.61</v>
       </c>
       <c r="R43" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T43" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V43" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.49</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z44" t="n">
         <v>3.28</v>
       </c>
-      <c r="U44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V44" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="N45" t="n">
-        <v>5.75</v>
+        <v>4.39</v>
       </c>
       <c r="O45" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="P45" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.91</v>
+        <v>5.66</v>
       </c>
       <c r="R45" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T45" t="n">
-        <v>2.97</v>
+        <v>2.76</v>
       </c>
       <c r="U45" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.39</v>
+        <v>1.87</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1.92</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG46" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="O47" t="n">
-        <v>2.01</v>
+        <v>6.25</v>
       </c>
       <c r="P47" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="S47" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="T47" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>5.75</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X47" t="n">
         <v>1.08</v>
       </c>
-      <c r="X47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y47" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.98</v>
+        <v>2.59</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.61</v>
+        <v>4.29</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P48" t="n">
         <v>2.05</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="R48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V48" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.5</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC48" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="O49" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T49" t="n">
         <v>2.8</v>
       </c>
-      <c r="P49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.56</v>
-      </c>
       <c r="U49" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="V49" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.6</v>
+        <v>3.37</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
         <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
-        <v>4.28</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.64</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z50" t="n">
         <v>2.8</v>
       </c>
-      <c r="U50" t="n">
+      <c r="AA50" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG50" t="n">
         <v>1.35</v>
       </c>
-      <c r="V50" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M55" t="n">
         <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O55" t="n">
         <v>2.02</v>
@@ -6981,7 +6981,7 @@
         <v>2.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="R55" t="n">
         <v>1.38</v>
@@ -7014,7 +7014,7 @@
         <v>1.97</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>3.2</v>
@@ -7029,7 +7029,7 @@
         <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH55" t="n">
         <v>2.49</v>
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M57" t="n">
         <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O57" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q57" t="n">
         <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T57" t="n">
         <v>2.95</v>
       </c>
-      <c r="T57" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U57" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="W57" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46090.89583333334</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.07</v>
+        <v>1.73</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.38</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="T12" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH12" t="n">
         <v>3.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.73</v>
+        <v>3.07</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="T13" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.1</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3.38</v>
+        <v>2.87</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
-        <v>2.49</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.24</v>
+        <v>3.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.87</v>
+        <v>3.38</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.28</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>3.64</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.86</v>
+        <v>2.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46090.5625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>3.64</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.85</v>
+        <v>3.86</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.35</v>
+        <v>2.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46090.5625</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.69</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>6.45</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2.11</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>3.69</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.2</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA30" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>3.9</v>
+        <v>2.42</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.58</v>
+        <v>4.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
         <v>1.22</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
         <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>2.03</v>
       </c>
       <c r="O32" t="n">
-        <v>2.53</v>
+        <v>3.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.25</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.38</v>
       </c>
-      <c r="V32" t="n">
-        <v>7</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46090.625</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,61 +4467,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3.3</v>
       </c>
-      <c r="N34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
         <v>1.8</v>
@@ -4530,10 +4530,10 @@
         <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.77</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
         <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
         <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.86</v>
+        <v>5.75</v>
       </c>
       <c r="O39" t="n">
-        <v>5.6</v>
+        <v>2.07</v>
       </c>
       <c r="P39" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.49</v>
+        <v>6.91</v>
       </c>
       <c r="R39" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S39" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="U39" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.13</v>
+        <v>2.39</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="N40" t="n">
-        <v>5.75</v>
+        <v>5.51</v>
       </c>
       <c r="O40" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="P40" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.91</v>
+        <v>6.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T40" t="n">
         <v>2.97</v>
@@ -5211,43 +5211,43 @@
         <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AB40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF40" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AG40" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH40" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N42" t="n">
         <v>1.55</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5.51</v>
-      </c>
       <c r="O42" t="n">
-        <v>2.14</v>
+        <v>6.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.9</v>
+        <v>2.11</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T42" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V42" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="W42" t="n">
         <v>1.02</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>3</v>
+        <v>4.29</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.21</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.23</v>
+        <v>1.05</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="P43" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.61</v>
+        <v>3.86</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="U43" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="P44" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>5.66</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S44" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="T44" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.71</v>
+        <v>2.33</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>4.39</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="T45" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V45" t="n">
-        <v>9.300000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>2.01</v>
+        <v>5.6</v>
       </c>
       <c r="P46" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.5</v>
+        <v>2.49</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="T46" t="n">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="U46" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="V46" t="n">
-        <v>5.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.98</v>
+        <v>2.59</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.61</v>
+        <v>4.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.4</v>
+        <v>1.92</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="O47" t="n">
-        <v>6.25</v>
+        <v>2.58</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.11</v>
+        <v>4.61</v>
       </c>
       <c r="R47" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="U47" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="W47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X47" t="n">
         <v>1.02</v>
       </c>
-      <c r="X47" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y47" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.05</v>
+        <v>1.7</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="M48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.9</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.56</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P50" t="n">
         <v>2.05</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="R50" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.5</v>
       </c>
-      <c r="S50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V50" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC50" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N55" t="n">
-        <v>6.5</v>
+        <v>6.42</v>
       </c>
       <c r="O55" t="n">
         <v>2.02</v>
@@ -6984,19 +6984,19 @@
         <v>5.75</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T55" t="n">
         <v>2.75</v>
       </c>
       <c r="U55" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V55" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="W55" t="n">
         <v>1.05</v>
@@ -7005,7 +7005,7 @@
         <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z55" t="n">
         <v>3.3</v>
@@ -7017,10 +7017,10 @@
         <v>1.85</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE55" t="n">
         <v>2.05</v>
@@ -7029,10 +7029,10 @@
         <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46090.83333333334</v>
@@ -7204,25 +7204,25 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N57" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="O57" t="n">
         <v>2.07</v>
       </c>
       <c r="P57" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="Q57" t="n">
         <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
         <v>2.62</v>
@@ -7243,25 +7243,25 @@
         <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF57" t="n">
         <v>1.74</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="N2" t="n">
         <v>2.24</v>
@@ -683,7 +683,7 @@
         <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -695,37 +695,37 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.74</v>
+        <v>5.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
         <v>2.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
         <v>1.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46090.33333333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.03</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>4.08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>3.17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.28</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>6.3</v>
+        <v>5.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.78</v>
+        <v>4.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
         <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46090.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.07</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH13" t="n">
         <v>3.35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46090.4375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>3.76</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46090.4375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46090.4375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46090.45833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46090.45833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>2.87</v>
       </c>
       <c r="O24" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
         <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.1</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH25" t="n">
-        <v>3.38</v>
+        <v>2.87</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46090.54166666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3875,70 +3875,70 @@
         <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46090.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.42</v>
-      </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.02</v>
+        <v>3.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4232,70 +4232,70 @@
         <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="T32" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>5.95</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.07</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46090.58333333334</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="O33" t="n">
         <v>2.6</v>
@@ -4363,22 +4363,22 @@
         <v>2.01</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.77</v>
+        <v>4.72</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="T33" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
         <v>1.32</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
         <v>1.03</v>
@@ -4387,28 +4387,28 @@
         <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
         <v>1.29</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,61 +4467,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
         <v>1.8</v>
@@ -4530,10 +4530,10 @@
         <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46090.625</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,61 +4586,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
         <v>1.8</v>
@@ -4649,10 +4649,10 @@
         <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46090.625</v>
@@ -4717,22 +4717,22 @@
         <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
         <v>2.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S36" t="n">
         <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V36" t="n">
         <v>5.25</v>
@@ -4756,13 +4756,13 @@
         <v>2.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AD36" t="n">
         <v>1.46</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
         <v>2.44</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.24</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
-        <v>6.7</v>
+        <v>4.33</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.92</v>
+        <v>2.09</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46090.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="M38" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>5.24</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="T38" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>4.33</v>
+        <v>6.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.59</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46090.66666666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
-        <v>2.07</v>
+        <v>2.58</v>
       </c>
       <c r="P39" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.91</v>
+        <v>4.61</v>
       </c>
       <c r="R39" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T39" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U39" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V39" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W39" t="n">
         <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
         <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46090.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.55</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH40" t="n">
-        <v>2.23</v>
+        <v>1.13</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46090.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>4.39</v>
       </c>
       <c r="O41" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="P41" t="n">
         <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.67</v>
+        <v>5.66</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S41" t="n">
         <v>2.36</v>
       </c>
       <c r="T41" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="U41" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z41" t="n">
         <v>2.62</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB41" t="n">
         <v>1.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46090.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="O42" t="n">
-        <v>6.25</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S42" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U42" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="V42" t="n">
-        <v>9.5</v>
+        <v>5.75</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z42" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE42" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46090.6875</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O43" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="P43" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA43" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q43" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.58</v>
+        <v>2.39</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46090.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>4.39</v>
+        <v>1.95</v>
       </c>
       <c r="O44" t="n">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="P44" t="n">
         <v>1.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.66</v>
+        <v>2.67</v>
       </c>
       <c r="R44" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S44" t="n">
         <v>2.36</v>
       </c>
       <c r="T44" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
         <v>2.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
         <v>1.55</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46090.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.5</v>
+        <v>3.86</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="U45" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="V45" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
         <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46090.6875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.3</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>5.51</v>
       </c>
       <c r="O46" t="n">
-        <v>5.6</v>
+        <v>2.14</v>
       </c>
       <c r="P46" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.49</v>
+        <v>6.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T46" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="U46" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V46" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
         <v>1.01</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y46" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.13</v>
+        <v>2.23</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46090.6875</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="O47" t="n">
-        <v>2.58</v>
+        <v>6.25</v>
       </c>
       <c r="P47" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.61</v>
+        <v>2.11</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S47" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T47" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V47" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.5</v>
+        <v>4.29</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.7</v>
+        <v>1.05</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46090.6875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="P48" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="R48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.5</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC48" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46090.69791666666</v>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O49" t="n">
         <v>4.28</v>
@@ -6288,7 +6288,7 @@
         <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
         <v>1.31</v>
@@ -6297,16 +6297,16 @@
         <v>3.37</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC49" t="n">
         <v>3.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE49" t="n">
         <v>1.73</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.9</v>
       </c>
-      <c r="N50" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.56</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46090.69791666666</v>

--- a/jogos_2026-03-09.xlsx
+++ b/jogos_2026-03-09.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="M2" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
         <v>3.76</v>
@@ -704,7 +704,7 @@
         <v>2.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="AB2" t="n">
         <v>1.37</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>3.05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>4.08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>3.17</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46090.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.9</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.08</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.17</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>5.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46090.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46090.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704